--- a/modules/translations/translations_de_2.xlsx
+++ b/modules/translations/translations_de_2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="421">
   <si>
     <t>DE</t>
   </si>
@@ -22,37 +22,97 @@
     <t>Translation</t>
   </si>
   <si>
-    <t>ablehnen</t>
+    <t>abbrechen</t>
+  </si>
+  <si>
+    <t>abnehmen</t>
   </si>
   <si>
     <t>abonnieren</t>
   </si>
   <si>
-    <t>abwenden</t>
-  </si>
-  <si>
-    <t>aktualisieren</t>
+    <t>abschreiben</t>
+  </si>
+  <si>
+    <t>absetzen</t>
+  </si>
+  <si>
+    <t>ahnen</t>
   </si>
   <si>
     <t>analysieren</t>
   </si>
   <si>
+    <t>anfehen</t>
+  </si>
+  <si>
+    <t>anführen</t>
+  </si>
+  <si>
     <t>angeben</t>
   </si>
   <si>
-    <t>appellieren</t>
-  </si>
-  <si>
-    <t>auferlegen</t>
+    <t>angefordert</t>
+  </si>
+  <si>
+    <t>angewiesen</t>
+  </si>
+  <si>
+    <t>anlegen</t>
+  </si>
+  <si>
+    <t>annullieren</t>
+  </si>
+  <si>
+    <t>anprangern</t>
+  </si>
+  <si>
+    <t>ansehen</t>
+  </si>
+  <si>
+    <t>ansprechen</t>
+  </si>
+  <si>
+    <t>auffliegen</t>
+  </si>
+  <si>
+    <t>aufhören</t>
+  </si>
+  <si>
+    <t>aufkaufen</t>
   </si>
   <si>
     <t>auflegen</t>
   </si>
   <si>
+    <t>auflisten</t>
+  </si>
+  <si>
+    <t>aufnehmen</t>
+  </si>
+  <si>
+    <t>auftreten</t>
+  </si>
+  <si>
+    <t>aufzudecken</t>
+  </si>
+  <si>
     <t>ausdrücken</t>
   </si>
   <si>
-    <t>aussprechen</t>
+    <t>aushebeln</t>
+  </si>
+  <si>
+    <t>ausnutzen</t>
+  </si>
+  <si>
+    <t>ausspionieren</t>
+  </si>
+  <si>
+    <t>ausweiten</t>
+  </si>
+  <si>
+    <t>ausüben</t>
   </si>
   <si>
     <t>beabsichtigen</t>
@@ -61,127 +121,193 @@
     <t>bedrohen</t>
   </si>
   <si>
-    <t>begründen</t>
-  </si>
-  <si>
-    <t>bekanntgeben</t>
-  </si>
-  <si>
-    <t>bemerken</t>
-  </si>
-  <si>
-    <t>beschleunigen</t>
+    <t>beenden</t>
+  </si>
+  <si>
+    <t>befehligen</t>
+  </si>
+  <si>
+    <t>befinden</t>
+  </si>
+  <si>
+    <t>befördern</t>
+  </si>
+  <si>
+    <t>begreifen</t>
+  </si>
+  <si>
+    <t>behandeln</t>
+  </si>
+  <si>
+    <t>behaupten</t>
+  </si>
+  <si>
+    <t>beitreten</t>
+  </si>
+  <si>
+    <t>bekommen</t>
+  </si>
+  <si>
+    <t>belügen</t>
   </si>
   <si>
     <t>beschließen</t>
   </si>
   <si>
-    <t>beschreiben</t>
-  </si>
-  <si>
-    <t>besetzen</t>
-  </si>
-  <si>
-    <t>besiegen</t>
-  </si>
-  <si>
-    <t>bestreben</t>
-  </si>
-  <si>
-    <t>blockieren</t>
-  </si>
-  <si>
-    <t>dementieren</t>
+    <t>bestehen</t>
+  </si>
+  <si>
+    <t>besuchen</t>
+  </si>
+  <si>
+    <t>betreiben</t>
+  </si>
+  <si>
+    <t>beweisen</t>
+  </si>
+  <si>
+    <t>bezeichnen</t>
+  </si>
+  <si>
+    <t>beziehen</t>
+  </si>
+  <si>
+    <t>bitten</t>
+  </si>
+  <si>
+    <t>brechen</t>
+  </si>
+  <si>
+    <t>codieren</t>
+  </si>
+  <si>
+    <t>darlegen</t>
+  </si>
+  <si>
+    <t>deklassieren</t>
+  </si>
+  <si>
+    <t>deklassifizieren</t>
   </si>
   <si>
     <t>dulden</t>
   </si>
   <si>
+    <t>durchdrücken</t>
+  </si>
+  <si>
+    <t>einberufen</t>
+  </si>
+  <si>
+    <t>einbeziehen</t>
+  </si>
+  <si>
+    <t>einbrechen</t>
+  </si>
+  <si>
+    <t>einführen</t>
+  </si>
+  <si>
+    <t>eingehen</t>
+  </si>
+  <si>
     <t>eingesehen</t>
   </si>
   <si>
-    <t>eingreifen</t>
+    <t>einkaufen</t>
+  </si>
+  <si>
+    <t>einschalten</t>
   </si>
   <si>
     <t>empfhieln</t>
   </si>
   <si>
-    <t>enden</t>
-  </si>
-  <si>
-    <t>enthalten</t>
+    <t>empfinden</t>
+  </si>
+  <si>
+    <t>entfesseln</t>
+  </si>
+  <si>
+    <t>entlassen</t>
   </si>
   <si>
     <t>entwerfen</t>
   </si>
   <si>
-    <t>ergreifen</t>
-  </si>
-  <si>
-    <t>ergänzen</t>
-  </si>
-  <si>
-    <t>erhalten</t>
-  </si>
-  <si>
-    <t>erheben</t>
-  </si>
-  <si>
-    <t>erhören</t>
-  </si>
-  <si>
-    <t>erinnern</t>
+    <t>erfahren</t>
+  </si>
+  <si>
+    <t>erfassen</t>
   </si>
   <si>
     <t>erlassen</t>
   </si>
   <si>
-    <t>erobern</t>
-  </si>
-  <si>
-    <t>erweitern</t>
-  </si>
-  <si>
-    <t>erzeugen</t>
-  </si>
-  <si>
-    <t>erzwingen</t>
+    <t>erließ</t>
+  </si>
+  <si>
+    <t>erreichen</t>
+  </si>
+  <si>
+    <t>errichten</t>
+  </si>
+  <si>
+    <t>erringen</t>
+  </si>
+  <si>
+    <t>erstellen</t>
+  </si>
+  <si>
+    <t>erteilen</t>
+  </si>
+  <si>
+    <t>erwecken</t>
+  </si>
+  <si>
+    <t>erwidern</t>
   </si>
   <si>
     <t>erzählen</t>
   </si>
   <si>
-    <t>eröffnen</t>
-  </si>
-  <si>
-    <t>feststellen</t>
-  </si>
-  <si>
-    <t>finden</t>
-  </si>
-  <si>
-    <t>fluten</t>
-  </si>
-  <si>
-    <t>folgen</t>
-  </si>
-  <si>
-    <t>formulieren</t>
+    <t>eskalieren</t>
+  </si>
+  <si>
+    <t>fassen</t>
+  </si>
+  <si>
+    <t>festnehmen</t>
+  </si>
+  <si>
+    <t>feuern</t>
   </si>
   <si>
     <t>fortsetzen</t>
   </si>
   <si>
-    <t>fragen</t>
-  </si>
-  <si>
-    <t>füllen</t>
-  </si>
-  <si>
-    <t>garantieren</t>
-  </si>
-  <si>
-    <t>gedenken</t>
+    <t>freisprechen</t>
+  </si>
+  <si>
+    <t>fällen</t>
+  </si>
+  <si>
+    <t>gelten</t>
+  </si>
+  <si>
+    <t>genesen</t>
+  </si>
+  <si>
+    <t>geschworen</t>
+  </si>
+  <si>
+    <t>getrennt</t>
+  </si>
+  <si>
+    <t>gratulieren</t>
+  </si>
+  <si>
+    <t>grüßen</t>
   </si>
   <si>
     <t>hacken</t>
@@ -190,28 +316,55 @@
     <t>heraufbeschwören</t>
   </si>
   <si>
-    <t>herausbringen</t>
-  </si>
-  <si>
-    <t>hervorgehen</t>
-  </si>
-  <si>
-    <t>integrieren</t>
-  </si>
-  <si>
-    <t>interessieren</t>
-  </si>
-  <si>
-    <t>isolieren</t>
-  </si>
-  <si>
-    <t>klären</t>
-  </si>
-  <si>
-    <t>kontrollieren</t>
-  </si>
-  <si>
-    <t>lesen</t>
+    <t>herausstellen</t>
+  </si>
+  <si>
+    <t>heucheln</t>
+  </si>
+  <si>
+    <t>hinterlassen</t>
+  </si>
+  <si>
+    <t>holen</t>
+  </si>
+  <si>
+    <t>identifizieren</t>
+  </si>
+  <si>
+    <t>ignorieren</t>
+  </si>
+  <si>
+    <t>infiltrieren</t>
+  </si>
+  <si>
+    <t>investieren</t>
+  </si>
+  <si>
+    <t>jucken</t>
+  </si>
+  <si>
+    <t>kapitulieren</t>
+  </si>
+  <si>
+    <t>kehren</t>
+  </si>
+  <si>
+    <t>killen</t>
+  </si>
+  <si>
+    <t>konspirieren</t>
+  </si>
+  <si>
+    <t>kontaktieren</t>
+  </si>
+  <si>
+    <t>kämpfen</t>
+  </si>
+  <si>
+    <t>launchen</t>
+  </si>
+  <si>
+    <t>launcht</t>
   </si>
   <si>
     <t>loben</t>
@@ -220,25 +373,43 @@
     <t>lächeln</t>
   </si>
   <si>
-    <t>mahnen</t>
+    <t>lässt</t>
+  </si>
+  <si>
+    <t>malen</t>
   </si>
   <si>
     <t>merken</t>
   </si>
   <si>
-    <t>nachgeben</t>
-  </si>
-  <si>
-    <t>nennen</t>
-  </si>
-  <si>
-    <t>plädieren</t>
-  </si>
-  <si>
-    <t>praktizieren</t>
-  </si>
-  <si>
-    <t>publizieren</t>
+    <t>missachten</t>
+  </si>
+  <si>
+    <t>missbrauchen</t>
+  </si>
+  <si>
+    <t>mitspieln</t>
+  </si>
+  <si>
+    <t>modifizieren</t>
+  </si>
+  <si>
+    <t>nominieren</t>
+  </si>
+  <si>
+    <t>organisieren</t>
+  </si>
+  <si>
+    <t>posieren</t>
+  </si>
+  <si>
+    <t>pushen</t>
+  </si>
+  <si>
+    <t>raten</t>
+  </si>
+  <si>
+    <t>rauchen</t>
   </si>
   <si>
     <t>recherchieren</t>
@@ -247,52 +418,115 @@
     <t>rechnen</t>
   </si>
   <si>
-    <t>reden</t>
-  </si>
-  <si>
-    <t>reiben</t>
-  </si>
-  <si>
-    <t>rennen</t>
-  </si>
-  <si>
-    <t>ruinieren</t>
-  </si>
-  <si>
-    <t>schlagen</t>
-  </si>
-  <si>
-    <t>senken</t>
-  </si>
-  <si>
-    <t>servieren</t>
-  </si>
-  <si>
-    <t>sicherstellen</t>
-  </si>
-  <si>
-    <t>singen</t>
-  </si>
-  <si>
-    <t>streichen</t>
-  </si>
-  <si>
-    <t>taumeln</t>
+    <t>regieren</t>
+  </si>
+  <si>
+    <t>regiert</t>
+  </si>
+  <si>
+    <t>relativieren</t>
+  </si>
+  <si>
+    <t>retweeten</t>
+  </si>
+  <si>
+    <t>sammeln</t>
+  </si>
+  <si>
+    <t>sanktionieren</t>
+  </si>
+  <si>
+    <t>schaden</t>
+  </si>
+  <si>
+    <t>schau</t>
+  </si>
+  <si>
+    <t>scheiden</t>
+  </si>
+  <si>
+    <t>scheinen</t>
+  </si>
+  <si>
+    <t>schicken</t>
+  </si>
+  <si>
+    <t>schickt</t>
+  </si>
+  <si>
+    <t>schmieren</t>
+  </si>
+  <si>
+    <t>schulden</t>
+  </si>
+  <si>
+    <t>schwächen</t>
+  </si>
+  <si>
+    <t>siegen</t>
+  </si>
+  <si>
+    <t>spekulieren</t>
+  </si>
+  <si>
+    <t>spielen</t>
+  </si>
+  <si>
+    <t>starren</t>
+  </si>
+  <si>
+    <t>stattfinden</t>
+  </si>
+  <si>
+    <t>steigern</t>
+  </si>
+  <si>
+    <t>stilllegen</t>
+  </si>
+  <si>
+    <t>streiten</t>
+  </si>
+  <si>
+    <t>stufen</t>
   </si>
   <si>
     <t>terrorisieren</t>
   </si>
   <si>
-    <t>untergräben</t>
-  </si>
-  <si>
-    <t>unternehmen</t>
-  </si>
-  <si>
-    <t>unterstellen</t>
-  </si>
-  <si>
-    <t>verbannen</t>
+    <t>testen</t>
+  </si>
+  <si>
+    <t>treffen</t>
+  </si>
+  <si>
+    <t>trinken</t>
+  </si>
+  <si>
+    <t>trockenlegen</t>
+  </si>
+  <si>
+    <t>twittern</t>
+  </si>
+  <si>
+    <t>töten</t>
+  </si>
+  <si>
+    <t>umstellen</t>
+  </si>
+  <si>
+    <t>untergehen</t>
+  </si>
+  <si>
+    <t>unterschreiben</t>
+  </si>
+  <si>
+    <t>unterzeichnen</t>
+  </si>
+  <si>
+    <t>veranstalten</t>
+  </si>
+  <si>
+    <t>verarschen</t>
   </si>
   <si>
     <t>verbieten</t>
@@ -301,112 +535,226 @@
     <t>vereiteln</t>
   </si>
   <si>
-    <t>vergisst</t>
-  </si>
-  <si>
-    <t>vergleichen</t>
-  </si>
-  <si>
-    <t>verhängen</t>
-  </si>
-  <si>
-    <t>verhöhnen</t>
-  </si>
-  <si>
-    <t>verkünden</t>
-  </si>
-  <si>
-    <t>verlassen</t>
-  </si>
-  <si>
-    <t>verlängern</t>
-  </si>
-  <si>
-    <t>vermeiden</t>
+    <t>verfallen</t>
+  </si>
+  <si>
+    <t>verleumden</t>
+  </si>
+  <si>
+    <t>verlässt</t>
   </si>
   <si>
     <t>verpflichten</t>
   </si>
   <si>
-    <t>verplappern</t>
+    <t>versagen</t>
+  </si>
+  <si>
+    <t>verschaffen</t>
   </si>
   <si>
     <t>verschweigen</t>
   </si>
   <si>
-    <t>verschwenden</t>
+    <t>verschwiegen</t>
+  </si>
+  <si>
+    <t>verschärfen</t>
+  </si>
+  <si>
+    <t>versehen</t>
+  </si>
+  <si>
+    <t>verselbständigen</t>
   </si>
   <si>
     <t>versorgen</t>
   </si>
   <si>
-    <t>versterben</t>
-  </si>
-  <si>
-    <t>vorbereiten</t>
-  </si>
-  <si>
-    <t>wagen</t>
-  </si>
-  <si>
-    <t>weiten</t>
+    <t>verspotten</t>
+  </si>
+  <si>
+    <t>verstummen</t>
+  </si>
+  <si>
+    <t>verweisen</t>
+  </si>
+  <si>
+    <t>verwerfen</t>
+  </si>
+  <si>
+    <t>verwischen</t>
+  </si>
+  <si>
+    <t>verzögern</t>
+  </si>
+  <si>
+    <t>vollbringen</t>
+  </si>
+  <si>
+    <t>vorgeben</t>
+  </si>
+  <si>
+    <t>vorschlagen</t>
+  </si>
+  <si>
+    <t>vorschreiben</t>
+  </si>
+  <si>
+    <t>vorstellen</t>
+  </si>
+  <si>
+    <t>wackeln</t>
+  </si>
+  <si>
+    <t>wegnehmen</t>
+  </si>
+  <si>
+    <t>weinen</t>
+  </si>
+  <si>
+    <t>werfen</t>
+  </si>
+  <si>
+    <t>widersprechen</t>
   </si>
   <si>
     <t>widmen</t>
   </si>
   <si>
+    <t>wiederholen</t>
+  </si>
+  <si>
+    <t>wählen</t>
+  </si>
+  <si>
     <t>zerfallen</t>
   </si>
   <si>
-    <t>zerschlagen</t>
-  </si>
-  <si>
-    <t>zugreifen</t>
+    <t>zielen</t>
+  </si>
+  <si>
+    <t>zurückkommen</t>
+  </si>
+  <si>
+    <t>zurücknehmen</t>
+  </si>
+  <si>
+    <t>zusagen</t>
+  </si>
+  <si>
+    <t>zusammenarbeiten</t>
+  </si>
+  <si>
+    <t>zustimmen</t>
   </si>
   <si>
     <t>zündeln</t>
   </si>
   <si>
-    <t>überführen</t>
-  </si>
-  <si>
-    <t>übersetzen</t>
+    <t>ändern</t>
+  </si>
+  <si>
+    <t>überleben</t>
+  </si>
+  <si>
+    <t>überlegen</t>
   </si>
   <si>
     <t>überstehen</t>
   </si>
   <si>
-    <t>reject</t>
+    <t>abort</t>
+  </si>
+  <si>
+    <t>decrease</t>
   </si>
   <si>
     <t>subscribe</t>
   </si>
   <si>
-    <t>avert</t>
-  </si>
-  <si>
-    <t>update</t>
+    <t>write off</t>
+  </si>
+  <si>
+    <t>set down</t>
+  </si>
+  <si>
+    <t>ancestor</t>
   </si>
   <si>
     <t>analyze</t>
   </si>
   <si>
+    <t>view/examine</t>
+  </si>
+  <si>
+    <t>to lead</t>
+  </si>
+  <si>
     <t>specify/state</t>
   </si>
   <si>
-    <t>appeal</t>
-  </si>
-  <si>
-    <t>impose</t>
+    <t>requested</t>
+  </si>
+  <si>
+    <t>instructed</t>
+  </si>
+  <si>
+    <t>create</t>
+  </si>
+  <si>
+    <t>annul</t>
+  </si>
+  <si>
+    <t>denounce</t>
+  </si>
+  <si>
+    <t>view</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>blow up</t>
+  </si>
+  <si>
+    <t>cease</t>
+  </si>
+  <si>
+    <t>buy up</t>
   </si>
   <si>
     <t>add on/apply</t>
   </si>
   <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>take in/include</t>
+  </si>
+  <si>
+    <t>occur</t>
+  </si>
+  <si>
+    <t>uncover</t>
+  </si>
+  <si>
     <t>express</t>
   </si>
   <si>
-    <t>pronounce</t>
+    <t>lever out</t>
+  </si>
+  <si>
+    <t>exploit</t>
+  </si>
+  <si>
+    <t>spy out</t>
+  </si>
+  <si>
+    <t>expand</t>
+  </si>
+  <si>
+    <t>exercise</t>
   </si>
   <si>
     <t>intend</t>
@@ -415,127 +763,187 @@
     <t>threaten</t>
   </si>
   <si>
-    <t>justify</t>
-  </si>
-  <si>
-    <t>announce</t>
-  </si>
-  <si>
-    <t>notice</t>
-  </si>
-  <si>
-    <t>accelerate</t>
+    <t>end</t>
+  </si>
+  <si>
+    <t>command</t>
+  </si>
+  <si>
+    <t>are</t>
+  </si>
+  <si>
+    <t>to promote</t>
+  </si>
+  <si>
+    <t>comprehend</t>
+  </si>
+  <si>
+    <t>treat</t>
+  </si>
+  <si>
+    <t>assert</t>
+  </si>
+  <si>
+    <t>join</t>
+  </si>
+  <si>
+    <t>get</t>
+  </si>
+  <si>
+    <t>lie</t>
   </si>
   <si>
     <t>decide</t>
   </si>
   <si>
-    <t>describe</t>
-  </si>
-  <si>
-    <t>occupy</t>
-  </si>
-  <si>
-    <t>defeat</t>
-  </si>
-  <si>
-    <t>endeavor</t>
-  </si>
-  <si>
-    <t>block</t>
-  </si>
-  <si>
-    <t>deny</t>
+    <t>exist</t>
+  </si>
+  <si>
+    <t>visit</t>
+  </si>
+  <si>
+    <t>operate</t>
+  </si>
+  <si>
+    <t>prove</t>
+  </si>
+  <si>
+    <t>denote</t>
+  </si>
+  <si>
+    <t>refer</t>
+  </si>
+  <si>
+    <t>ask</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>encode</t>
+  </si>
+  <si>
+    <t>expose</t>
+  </si>
+  <si>
+    <t>declassify</t>
   </si>
   <si>
     <t>tolerate</t>
   </si>
   <si>
+    <t>push through</t>
+  </si>
+  <si>
+    <t>convene</t>
+  </si>
+  <si>
+    <t>include</t>
+  </si>
+  <si>
+    <t>break in</t>
+  </si>
+  <si>
+    <t>introduce</t>
+  </si>
+  <si>
+    <t>enter</t>
+  </si>
+  <si>
     <t>viewed</t>
   </si>
   <si>
-    <t>intervene</t>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>turn on</t>
   </si>
   <si>
     <t>recommend</t>
   </si>
   <si>
-    <t>end</t>
-  </si>
-  <si>
-    <t>contain/abstain</t>
+    <t>feel</t>
+  </si>
+  <si>
+    <t>unleash</t>
+  </si>
+  <si>
+    <t>dismissed</t>
   </si>
   <si>
     <t>design</t>
   </si>
   <si>
-    <t>seize</t>
-  </si>
-  <si>
-    <t>complement</t>
-  </si>
-  <si>
-    <t>receive</t>
-  </si>
-  <si>
-    <t>collect/raise</t>
-  </si>
-  <si>
-    <t>hear</t>
-  </si>
-  <si>
-    <t>recall</t>
+    <t>learn</t>
+  </si>
+  <si>
+    <t>capture</t>
   </si>
   <si>
     <t>enact/decree</t>
   </si>
   <si>
+    <t>enact</t>
+  </si>
+  <si>
+    <t>achieve</t>
+  </si>
+  <si>
+    <t>erect</t>
+  </si>
+  <si>
     <t>conquer</t>
   </si>
   <si>
-    <t>expand</t>
-  </si>
-  <si>
-    <t>generate</t>
-  </si>
-  <si>
-    <t>force</t>
+    <t>issue</t>
+  </si>
+  <si>
+    <t>awaken</t>
+  </si>
+  <si>
+    <t>reply</t>
   </si>
   <si>
     <t>tell</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>determine</t>
-  </si>
-  <si>
-    <t>find</t>
-  </si>
-  <si>
-    <t>flood</t>
-  </si>
-  <si>
-    <t>follow</t>
-  </si>
-  <si>
-    <t>formulate</t>
+    <t>escalate</t>
+  </si>
+  <si>
+    <t>grasp</t>
+  </si>
+  <si>
+    <t>arrest</t>
+  </si>
+  <si>
+    <t>fire</t>
   </si>
   <si>
     <t>continue</t>
   </si>
   <si>
-    <t>ask</t>
-  </si>
-  <si>
-    <t>fill</t>
-  </si>
-  <si>
-    <t>guarantee</t>
-  </si>
-  <si>
-    <t>commemorate</t>
+    <t>absolve</t>
+  </si>
+  <si>
+    <t>fall</t>
+  </si>
+  <si>
+    <t>apply</t>
+  </si>
+  <si>
+    <t>recover</t>
+  </si>
+  <si>
+    <t>sworn</t>
+  </si>
+  <si>
+    <t>separated</t>
+  </si>
+  <si>
+    <t>congratulate</t>
+  </si>
+  <si>
+    <t>greet</t>
   </si>
   <si>
     <t>hack</t>
@@ -544,28 +952,52 @@
     <t>conjure up</t>
   </si>
   <si>
-    <t>bring out/release</t>
-  </si>
-  <si>
-    <t>emerge</t>
-  </si>
-  <si>
-    <t>integrate</t>
-  </si>
-  <si>
-    <t>interest</t>
-  </si>
-  <si>
-    <t>isolate</t>
-  </si>
-  <si>
-    <t>clarify</t>
-  </si>
-  <si>
-    <t>control</t>
-  </si>
-  <si>
-    <t>read</t>
+    <t>emphasize</t>
+  </si>
+  <si>
+    <t>dissemble</t>
+  </si>
+  <si>
+    <t>leave behind</t>
+  </si>
+  <si>
+    <t>identify</t>
+  </si>
+  <si>
+    <t>ignore</t>
+  </si>
+  <si>
+    <t>infiltrate</t>
+  </si>
+  <si>
+    <t>invest</t>
+  </si>
+  <si>
+    <t>itch</t>
+  </si>
+  <si>
+    <t>surrender</t>
+  </si>
+  <si>
+    <t>sweep</t>
+  </si>
+  <si>
+    <t>kill</t>
+  </si>
+  <si>
+    <t>conspire</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>fight</t>
+  </si>
+  <si>
+    <t>launch</t>
+  </si>
+  <si>
+    <t>launches</t>
   </si>
   <si>
     <t>praise</t>
@@ -574,25 +1006,43 @@
     <t>smile</t>
   </si>
   <si>
-    <t>admonish</t>
+    <t>lets</t>
+  </si>
+  <si>
+    <t>paint</t>
   </si>
   <si>
     <t>memorize</t>
   </si>
   <si>
-    <t>yield</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>plead</t>
-  </si>
-  <si>
-    <t>practise</t>
-  </si>
-  <si>
-    <t>publish</t>
+    <t>disregard</t>
+  </si>
+  <si>
+    <t>abuse</t>
+  </si>
+  <si>
+    <t>play along</t>
+  </si>
+  <si>
+    <t>modify</t>
+  </si>
+  <si>
+    <t>nominate</t>
+  </si>
+  <si>
+    <t>organize</t>
+  </si>
+  <si>
+    <t>pose</t>
+  </si>
+  <si>
+    <t>push</t>
+  </si>
+  <si>
+    <t>guess</t>
+  </si>
+  <si>
+    <t>smoke</t>
   </si>
   <si>
     <t>research</t>
@@ -601,52 +1051,103 @@
     <t>calculate</t>
   </si>
   <si>
-    <t>speak</t>
-  </si>
-  <si>
-    <t>rub</t>
-  </si>
-  <si>
-    <t>run</t>
-  </si>
-  <si>
-    <t>ruin</t>
-  </si>
-  <si>
-    <t>beat</t>
-  </si>
-  <si>
-    <t>lower/reduce</t>
-  </si>
-  <si>
-    <t>serve</t>
-  </si>
-  <si>
-    <t>ensure</t>
-  </si>
-  <si>
-    <t>sing</t>
-  </si>
-  <si>
-    <t>delete</t>
-  </si>
-  <si>
-    <t>stagger</t>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>governs</t>
+  </si>
+  <si>
+    <t>relativize</t>
+  </si>
+  <si>
+    <t>retweet</t>
+  </si>
+  <si>
+    <t>collect</t>
+  </si>
+  <si>
+    <t>sanction</t>
+  </si>
+  <si>
+    <t>harm</t>
+  </si>
+  <si>
+    <t>look</t>
+  </si>
+  <si>
+    <t>divorce</t>
+  </si>
+  <si>
+    <t>seem</t>
+  </si>
+  <si>
+    <t>send</t>
+  </si>
+  <si>
+    <t>sends</t>
+  </si>
+  <si>
+    <t>smear</t>
+  </si>
+  <si>
+    <t>debt</t>
+  </si>
+  <si>
+    <t>weaken</t>
+  </si>
+  <si>
+    <t>speculate</t>
+  </si>
+  <si>
+    <t>play</t>
+  </si>
+  <si>
+    <t>stare</t>
+  </si>
+  <si>
+    <t>take place</t>
+  </si>
+  <si>
+    <t>increase</t>
+  </si>
+  <si>
+    <t>shut down</t>
+  </si>
+  <si>
+    <t>argue</t>
+  </si>
+  <si>
+    <t>level</t>
   </si>
   <si>
     <t>terrorize</t>
   </si>
   <si>
-    <t>undermine</t>
-  </si>
-  <si>
-    <t>undertake</t>
-  </si>
-  <si>
-    <t>insinuate/allege</t>
-  </si>
-  <si>
-    <t>banish</t>
+    <t>test</t>
+  </si>
+  <si>
+    <t>meet</t>
+  </si>
+  <si>
+    <t>drink</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>tweet</t>
+  </si>
+  <si>
+    <t>convert</t>
+  </si>
+  <si>
+    <t>perish</t>
+  </si>
+  <si>
+    <t>sign</t>
+  </si>
+  <si>
+    <t>take the piss</t>
   </si>
   <si>
     <t>forbid</t>
@@ -655,76 +1156,127 @@
     <t>thwart</t>
   </si>
   <si>
-    <t>forgets</t>
-  </si>
-  <si>
-    <t>compare</t>
+    <t>forfeit</t>
+  </si>
+  <si>
+    <t>slander</t>
+  </si>
+  <si>
+    <t>leaves</t>
+  </si>
+  <si>
+    <t>oblige</t>
+  </si>
+  <si>
+    <t>fail</t>
+  </si>
+  <si>
+    <t>procure</t>
+  </si>
+  <si>
+    <t>conceal</t>
+  </si>
+  <si>
+    <t>conceal/hide</t>
+  </si>
+  <si>
+    <t>exacerbate/aggravate</t>
+  </si>
+  <si>
+    <t>provided</t>
+  </si>
+  <si>
+    <t>become independent</t>
+  </si>
+  <si>
+    <t>provide</t>
   </si>
   <si>
     <t>mock</t>
   </si>
   <si>
-    <t>proclaim</t>
-  </si>
-  <si>
-    <t>leave</t>
-  </si>
-  <si>
-    <t>prolong</t>
-  </si>
-  <si>
-    <t>avoid</t>
-  </si>
-  <si>
-    <t>oblige</t>
-  </si>
-  <si>
-    <t>blab</t>
-  </si>
-  <si>
-    <t>conceal</t>
-  </si>
-  <si>
-    <t>waste</t>
-  </si>
-  <si>
-    <t>provide</t>
-  </si>
-  <si>
-    <t>die</t>
-  </si>
-  <si>
-    <t>prepare</t>
-  </si>
-  <si>
-    <t>dare</t>
-  </si>
-  <si>
-    <t>wide</t>
+    <t>fall silent</t>
+  </si>
+  <si>
+    <t>discard</t>
+  </si>
+  <si>
+    <t>blur</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>accomplish</t>
+  </si>
+  <si>
+    <t>pretend</t>
+  </si>
+  <si>
+    <t>propose</t>
+  </si>
+  <si>
+    <t>prescribe</t>
+  </si>
+  <si>
+    <t>imagine</t>
+  </si>
+  <si>
+    <t>wobble</t>
+  </si>
+  <si>
+    <t>take away</t>
+  </si>
+  <si>
+    <t>cry</t>
+  </si>
+  <si>
+    <t>throw</t>
+  </si>
+  <si>
+    <t>contradict</t>
   </si>
   <si>
     <t>dedicate</t>
   </si>
   <si>
+    <t>repeat</t>
+  </si>
+  <si>
+    <t>choose</t>
+  </si>
+  <si>
     <t>disintegrate</t>
   </si>
   <si>
-    <t>smash</t>
-  </si>
-  <si>
-    <t>access</t>
+    <t>aim</t>
+  </si>
+  <si>
+    <t>come back</t>
+  </si>
+  <si>
+    <t>take back</t>
+  </si>
+  <si>
+    <t>to promise</t>
+  </si>
+  <si>
+    <t>work together</t>
+  </si>
+  <si>
+    <t>agree</t>
   </si>
   <si>
     <t>ignite/play with fire</t>
   </si>
   <si>
-    <t>transfer</t>
-  </si>
-  <si>
-    <t>translate</t>
+    <t>change</t>
   </si>
   <si>
     <t>survive</t>
+  </si>
+  <si>
+    <t>superior</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1098,7 +1650,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1106,7 +1658,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1114,7 +1666,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1122,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1130,7 +1682,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1138,7 +1690,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1146,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1154,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1162,7 +1714,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1170,7 +1722,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1178,7 +1730,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1186,7 +1738,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1194,7 +1746,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1202,7 +1754,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1210,7 +1762,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1218,7 +1770,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1226,7 +1778,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1234,7 +1786,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1242,7 +1794,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1250,7 +1802,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1258,7 +1810,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1266,7 +1818,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>141</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1274,7 +1826,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1282,7 +1834,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1290,7 +1842,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1298,7 +1850,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1306,7 +1858,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1314,7 +1866,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1322,7 +1874,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1330,7 +1882,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1338,7 +1890,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1346,7 +1898,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1354,7 +1906,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1362,7 +1914,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1370,7 +1922,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1378,7 +1930,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1386,7 +1938,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1394,7 +1946,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1402,7 +1954,7 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1410,7 +1962,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1418,7 +1970,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>160</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1426,7 +1978,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>161</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1434,7 +1986,7 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>162</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1442,7 +1994,7 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1450,7 +2002,7 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1458,7 +2010,7 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1466,7 +2018,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>262</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1474,7 +2026,7 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1482,7 +2034,7 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>168</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1490,7 +2042,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>169</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1498,7 +2050,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>170</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1506,7 +2058,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1514,7 +2066,7 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>172</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1522,7 +2074,7 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1530,7 +2082,7 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>174</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1538,7 +2090,7 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1546,7 +2098,7 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>176</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1554,7 +2106,7 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>177</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1562,7 +2114,7 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>178</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1570,7 +2122,7 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>274</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1578,7 +2130,7 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>180</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1586,7 +2138,7 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>181</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1594,7 +2146,7 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>182</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1602,7 +2154,7 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>183</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1610,7 +2162,7 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>184</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1618,7 +2170,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>280</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1626,7 +2178,7 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>186</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1634,7 +2186,7 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>187</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1642,7 +2194,7 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>188</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1650,7 +2202,7 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1658,7 +2210,7 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>190</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1666,7 +2218,7 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>191</v>
+        <v>286</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1674,7 +2226,7 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1682,7 +2234,7 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1690,7 +2242,7 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>194</v>
+        <v>289</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1698,7 +2250,7 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>195</v>
+        <v>290</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1706,7 +2258,7 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>196</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1714,7 +2266,7 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>292</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1722,7 +2274,7 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1730,7 +2282,7 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1738,7 +2290,7 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>200</v>
+        <v>294</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1746,7 +2298,7 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1754,7 +2306,7 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>202</v>
+        <v>296</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1762,7 +2314,7 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1770,7 +2322,7 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>204</v>
+        <v>298</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1778,7 +2330,7 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>205</v>
+        <v>299</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1786,7 +2338,7 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1794,7 +2346,7 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1802,7 +2354,7 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>208</v>
+        <v>302</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1810,7 +2362,7 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>209</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1818,7 +2370,7 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>210</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1826,7 +2378,7 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>211</v>
+        <v>305</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1834,7 +2386,7 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>212</v>
+        <v>306</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1842,7 +2394,7 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>213</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1850,7 +2402,7 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>214</v>
+        <v>308</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1858,7 +2410,7 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1866,7 +2418,7 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>215</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1874,7 +2426,7 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>311</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1882,7 +2434,7 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>217</v>
+        <v>312</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1890,7 +2442,7 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>218</v>
+        <v>313</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1898,7 +2450,7 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>314</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1906,7 +2458,7 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1914,7 +2466,7 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>221</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1922,7 +2474,7 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>222</v>
+        <v>316</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1930,7 +2482,7 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>223</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1938,7 +2490,7 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>224</v>
+        <v>318</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1946,7 +2498,7 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>225</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1954,7 +2506,7 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>226</v>
+        <v>320</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1962,7 +2514,7 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>227</v>
+        <v>321</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1970,7 +2522,7 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>228</v>
+        <v>322</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1978,7 +2530,7 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1986,7 +2538,7 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>230</v>
+        <v>324</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1994,7 +2546,7 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>231</v>
+        <v>325</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2002,7 +2554,7 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>232</v>
+        <v>326</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2010,7 +2562,7 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>233</v>
+        <v>327</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2018,7 +2570,7 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>234</v>
+        <v>328</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2026,7 +2578,7 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>235</v>
+        <v>329</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2034,7 +2586,775 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>236</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+      <c r="B123" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>135</v>
+      </c>
+      <c r="B135" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>137</v>
+      </c>
+      <c r="B137" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>138</v>
+      </c>
+      <c r="B138" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>139</v>
+      </c>
+      <c r="B139" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>141</v>
+      </c>
+      <c r="B141" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>142</v>
+      </c>
+      <c r="B142" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>143</v>
+      </c>
+      <c r="B143" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>144</v>
+      </c>
+      <c r="B144" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>145</v>
+      </c>
+      <c r="B145" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>146</v>
+      </c>
+      <c r="B146" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>147</v>
+      </c>
+      <c r="B147" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>148</v>
+      </c>
+      <c r="B148" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>150</v>
+      </c>
+      <c r="B150" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>152</v>
+      </c>
+      <c r="B152" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>159</v>
+      </c>
+      <c r="B159" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>160</v>
+      </c>
+      <c r="B160" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>163</v>
+      </c>
+      <c r="B163" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>164</v>
+      </c>
+      <c r="B164" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>167</v>
+      </c>
+      <c r="B167" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>170</v>
+      </c>
+      <c r="B170" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>171</v>
+      </c>
+      <c r="B171" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>173</v>
+      </c>
+      <c r="B173" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>176</v>
+      </c>
+      <c r="B176" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>177</v>
+      </c>
+      <c r="B177" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" t="s">
+        <v>187</v>
+      </c>
+      <c r="B187" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" t="s">
+        <v>189</v>
+      </c>
+      <c r="B189" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" t="s">
+        <v>190</v>
+      </c>
+      <c r="B190" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" t="s">
+        <v>191</v>
+      </c>
+      <c r="B191" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" t="s">
+        <v>193</v>
+      </c>
+      <c r="B193" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" t="s">
+        <v>197</v>
+      </c>
+      <c r="B197" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" t="s">
+        <v>200</v>
+      </c>
+      <c r="B200" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" t="s">
+        <v>201</v>
+      </c>
+      <c r="B201" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>204</v>
+      </c>
+      <c r="B204" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" t="s">
+        <v>205</v>
+      </c>
+      <c r="B205" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" t="s">
+        <v>209</v>
+      </c>
+      <c r="B209" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>
